--- a/fisher_for_all_data.xlsx
+++ b/fisher_for_all_data.xlsx
@@ -583,31 +583,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoliosis</t>
+          <t>Alzheimer's Disease</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CNCCs</t>
+          <t>Cortical_organoids_d100</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.608940531763751</v>
+        <v>0.6683710831609646</v>
       </c>
       <c r="D3" t="n">
-        <v>1.989960515490272e-05</v>
+        <v>2.195838542923922e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>208</v>
+        <v>562</v>
       </c>
       <c r="G3" t="n">
-        <v>3411</v>
+        <v>2770</v>
       </c>
       <c r="H3" t="n">
-        <v>7713</v>
+        <v>7432</v>
       </c>
       <c r="I3" t="n">
         <v>0.000431848246775038</v>
@@ -616,25 +616,25 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1.082601054481547</v>
+        <v>1.12472487160675</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6749014804308221</v>
+        <v>0.5444108617705408</v>
       </c>
       <c r="M3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N3" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O3" t="n">
-        <v>1707</v>
+        <v>1363</v>
       </c>
       <c r="P3" t="n">
-        <v>1704</v>
+        <v>1407</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9408173212354329</v>
+        <v>0.9221139444327839</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
@@ -643,31 +643,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alzheimer's Disease</t>
+          <t>Scoliosis</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d100</t>
+          <t>CNCCs</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6683710831609646</v>
+        <v>1.608940531763751</v>
       </c>
       <c r="D4" t="n">
-        <v>2.195838542923922e-05</v>
+        <v>1.989960515490272e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F4" t="n">
-        <v>562</v>
+        <v>208</v>
       </c>
       <c r="G4" t="n">
-        <v>2770</v>
+        <v>3411</v>
       </c>
       <c r="H4" t="n">
-        <v>7432</v>
+        <v>7713</v>
       </c>
       <c r="I4" t="n">
         <v>0.000431848246775038</v>
@@ -676,25 +676,25 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.12472487160675</v>
+        <v>1.082601054481547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5444108617705408</v>
+        <v>0.6749014804308221</v>
       </c>
       <c r="M4" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O4" t="n">
-        <v>1363</v>
+        <v>1707</v>
       </c>
       <c r="P4" t="n">
-        <v>1407</v>
+        <v>1704</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9221139444327839</v>
+        <v>0.9408173212354329</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -1063,31 +1063,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ovarian polycystic syndrome (PCOS)</t>
+          <t>Back Disorders</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d50</t>
+          <t>4_Prechondral_Mesenchyme</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1773528847996933</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07437721465595361</v>
+        <v>0.07907646134494326</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="G11" t="n">
-        <v>3478</v>
+        <v>386</v>
       </c>
       <c r="H11" t="n">
-        <v>7402</v>
+        <v>9300</v>
       </c>
       <c r="I11" t="n">
         <v>0.3883549313822752</v>
@@ -1107,31 +1107,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alzheimer's Disease</t>
+          <t>Ovarian polycystic syndrome (PCOS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d150</t>
+          <t>Cortical_organoids_d50</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8544395223420647</v>
+        <v>0.1773528847996933</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08556973064355217</v>
+        <v>0.07437721465595361</v>
       </c>
       <c r="E12" t="n">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>528</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>2714</v>
+        <v>3478</v>
       </c>
       <c r="H12" t="n">
-        <v>7245</v>
+        <v>7402</v>
       </c>
       <c r="I12" t="n">
         <v>0.3883549313822752</v>
@@ -1139,30 +1139,14 @@
       <c r="J12" t="b">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>1.052989616899391</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.7517813221899442</v>
-      </c>
-      <c r="M12" t="n">
-        <v>85</v>
-      </c>
-      <c r="N12" t="n">
-        <v>84</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1330</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1384</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.9408173212354329</v>
-      </c>
-      <c r="R12" t="b">
-        <v>0</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1227,31 +1211,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Back Disorders</t>
+          <t>Alzheimer's Disease</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4_Prechondral_Mesenchyme</t>
+          <t>Cortical_organoids_d150</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.8544395223420647</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07907646134494326</v>
+        <v>0.08556973064355217</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="G14" t="n">
-        <v>386</v>
+        <v>2714</v>
       </c>
       <c r="H14" t="n">
-        <v>9300</v>
+        <v>7245</v>
       </c>
       <c r="I14" t="n">
         <v>0.3883549313822752</v>
@@ -1259,14 +1243,30 @@
       <c r="J14" t="b">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>1.052989616899391</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7517813221899442</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85</v>
+      </c>
+      <c r="N14" t="n">
+        <v>84</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1330</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1384</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.9408173212354329</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1331,31 +1331,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>carcinoma</t>
+          <t>Muscular dystrophy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pancreatic_progenitor_(PP)</t>
+          <t>Skeletal_myocyte_(SKM)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.108819359601728</v>
+        <v>0.5499887881602973</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1110302720267702</v>
+        <v>0.1061957063384298</v>
       </c>
       <c r="E16" t="n">
-        <v>471</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>569</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>5649</v>
+        <v>3021</v>
       </c>
       <c r="H16" t="n">
-        <v>7567</v>
+        <v>11446</v>
       </c>
       <c r="I16" t="n">
         <v>0.4094241280987149</v>
@@ -1363,59 +1363,43 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>0.9876987447698745</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.9236011123687078</v>
-      </c>
-      <c r="M16" t="n">
-        <v>232</v>
-      </c>
-      <c r="N16" t="n">
-        <v>239</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2800</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2849</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.9591242320751966</v>
-      </c>
-      <c r="R16" t="b">
-        <v>0</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Muscular dystrophy</t>
+          <t>carcinoma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Skeletal_myocyte_(SKM)</t>
+          <t>Pancreatic_progenitor_(PP)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5499887881602973</v>
+        <v>1.108819359601728</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1061957063384298</v>
+        <v>0.1110302720267702</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>471</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>569</v>
       </c>
       <c r="G17" t="n">
-        <v>3021</v>
+        <v>5649</v>
       </c>
       <c r="H17" t="n">
-        <v>11446</v>
+        <v>7567</v>
       </c>
       <c r="I17" t="n">
         <v>0.4094241280987149</v>
@@ -1423,14 +1407,30 @@
       <c r="J17" t="b">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0.9876987447698745</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9236011123687078</v>
+      </c>
+      <c r="M17" t="n">
+        <v>232</v>
+      </c>
+      <c r="N17" t="n">
+        <v>239</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2800</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2849</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.9591242320751966</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1495,31 +1495,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colon diverticulosis</t>
+          <t>Bipolar disorder</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Skeletal_myocyte_(SKM)</t>
+          <t>Cortical_organoids_d100</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.463838487094301</v>
+        <v>0.8306901905434015</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1470466708278776</v>
+        <v>0.181724572324664</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>250</v>
       </c>
       <c r="G19" t="n">
-        <v>3010</v>
+        <v>2834</v>
       </c>
       <c r="H19" t="n">
-        <v>11456</v>
+        <v>7744</v>
       </c>
       <c r="I19" t="n">
         <v>0.4467395736314655</v>
@@ -1528,25 +1528,25 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8236363636363636</v>
+        <v>0.6257920125814695</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8232465332793673</v>
+        <v>0.04894373111450499</v>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="N19" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="O19" t="n">
-        <v>1500</v>
+        <v>1407</v>
       </c>
       <c r="P19" t="n">
-        <v>1510</v>
+        <v>1427</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9408173212354329</v>
+        <v>0.2870649952337803</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
@@ -1555,31 +1555,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bipolar disorder</t>
+          <t>Colon diverticulosis</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d100</t>
+          <t>Skeletal_myocyte_(SKM)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.8306901905434015</v>
+        <v>1.463838487094301</v>
       </c>
       <c r="D20" t="n">
-        <v>0.181724572324664</v>
+        <v>0.1470466708278776</v>
       </c>
       <c r="E20" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>250</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>2834</v>
+        <v>3010</v>
       </c>
       <c r="H20" t="n">
-        <v>7744</v>
+        <v>11456</v>
       </c>
       <c r="I20" t="n">
         <v>0.4467395736314655</v>
@@ -1588,25 +1588,25 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6257920125814695</v>
+        <v>0.8236363636363636</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04894373111450499</v>
+        <v>0.8232465332793673</v>
       </c>
       <c r="M20" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="N20" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="O20" t="n">
-        <v>1407</v>
+        <v>1500</v>
       </c>
       <c r="P20" t="n">
-        <v>1427</v>
+        <v>1510</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2870649952337803</v>
+        <v>0.9408173212354329</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
@@ -1615,31 +1615,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>carcinoma</t>
+          <t>Varicose veins</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pooled_epidermis</t>
+          <t>Endothelial_not_treated</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.7342389374245329</v>
+        <v>0.3048483598101919</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1771624268749524</v>
+        <v>0.1416314841859758</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>741</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>380</v>
+        <v>4847</v>
       </c>
       <c r="H21" t="n">
-        <v>8989</v>
+        <v>7388</v>
       </c>
       <c r="I21" t="n">
         <v>0.4467395736314655</v>
@@ -1647,59 +1647,43 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
-      <c r="K21" t="n">
-        <v>2.486656200941915</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.0531601843025519</v>
-      </c>
-      <c r="M21" t="n">
-        <v>16</v>
-      </c>
-      <c r="N21" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>182</v>
-      </c>
-      <c r="P21" t="n">
-        <v>198</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2870649952337803</v>
-      </c>
-      <c r="R21" t="b">
-        <v>0</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Osteoarthritis</t>
+          <t>carcinoma</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4_Prechondral_Mesenchyme</t>
+          <t>Pooled_epidermis</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.7342389374245329</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1759116570297418</v>
+        <v>0.1771624268749524</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
-        <v>60</v>
+        <v>741</v>
       </c>
       <c r="G22" t="n">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H22" t="n">
-        <v>9322</v>
+        <v>8989</v>
       </c>
       <c r="I22" t="n">
         <v>0.4467395736314655</v>
@@ -1707,14 +1691,30 @@
       <c r="J22" t="b">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>2.486656200941915</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0531601843025519</v>
+      </c>
+      <c r="M22" t="n">
+        <v>16</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>182</v>
+      </c>
+      <c r="P22" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2870649952337803</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1823,31 +1823,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Varicose veins</t>
+          <t>Osteoarthritis</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Endothelial_not_treated</t>
+          <t>4_Prechondral_Mesenchyme</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3048483598101919</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1416314841859758</v>
+        <v>0.1759116570297418</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>4847</v>
+        <v>386</v>
       </c>
       <c r="H25" t="n">
-        <v>7388</v>
+        <v>9322</v>
       </c>
       <c r="I25" t="n">
         <v>0.4467395736314655</v>
@@ -2163,31 +2163,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alzheimer's Disease</t>
+          <t>Ovarian polycystic syndrome (PCOS)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d50</t>
+          <t>Skeletal_myocyte_(SKM)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9302362362864961</v>
+        <v>0.4744055482166447</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4029007018739673</v>
+        <v>0.3974935686153851</v>
       </c>
       <c r="E32" t="n">
-        <v>214</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>488</v>
+        <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>3265</v>
+        <v>3028</v>
       </c>
       <c r="H32" t="n">
-        <v>6926</v>
+        <v>11492</v>
       </c>
       <c r="I32" t="n">
         <v>0.7428481690801272</v>
@@ -2195,59 +2195,43 @@
       <c r="J32" t="b">
         <v>0</v>
       </c>
-      <c r="K32" t="n">
-        <v>1.088241620362072</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.5726477153681263</v>
-      </c>
-      <c r="M32" t="n">
-        <v>109</v>
-      </c>
-      <c r="N32" t="n">
-        <v>105</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1594</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.9221139444327839</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ovarian polycystic syndrome (PCOS)</t>
+          <t>Alzheimer's Disease</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Skeletal_myocyte_(SKM)</t>
+          <t>Cortical_organoids_d50</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.4744055482166447</v>
+        <v>0.9302362362864961</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3974935686153851</v>
+        <v>0.4029007018739673</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>214</v>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>488</v>
       </c>
       <c r="G33" t="n">
-        <v>3028</v>
+        <v>3265</v>
       </c>
       <c r="H33" t="n">
-        <v>11492</v>
+        <v>6926</v>
       </c>
       <c r="I33" t="n">
         <v>0.7428481690801272</v>
@@ -2255,43 +2239,59 @@
       <c r="J33" t="b">
         <v>0</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>1.088241620362072</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.5726477153681263</v>
+      </c>
+      <c r="M33" t="n">
+        <v>109</v>
+      </c>
+      <c r="N33" t="n">
+        <v>105</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1594</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.9221139444327839</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Scoliosis</t>
+          <t>Osteoarthritis</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Skeletal_myocyte_(SKM)</t>
+          <t>9_Chondrocytes</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9116883268459783</v>
+        <v>1.585354896675651</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4717008145713483</v>
+        <v>0.4753843662171084</v>
       </c>
       <c r="E34" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>349</v>
+        <v>42</v>
       </c>
       <c r="G34" t="n">
-        <v>2946</v>
+        <v>106</v>
       </c>
       <c r="H34" t="n">
-        <v>11159</v>
+        <v>7058</v>
       </c>
       <c r="I34" t="n">
         <v>0.8249316943179235</v>
@@ -2299,59 +2299,43 @@
       <c r="J34" t="b">
         <v>0</v>
       </c>
-      <c r="K34" t="n">
-        <v>0.8702040816326531</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.5805902613095306</v>
-      </c>
-      <c r="M34" t="n">
-        <v>39</v>
-      </c>
-      <c r="N34" t="n">
-        <v>45</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1470</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1476</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.9221139444327839</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Osteoarthritis</t>
+          <t>Scoliosis</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9_Chondrocytes</t>
+          <t>Skeletal_myocyte_(SKM)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.585354896675651</v>
+        <v>0.9116883268459783</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4753843662171084</v>
+        <v>0.4717008145713483</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="F35" t="n">
-        <v>42</v>
+        <v>349</v>
       </c>
       <c r="G35" t="n">
-        <v>106</v>
+        <v>2946</v>
       </c>
       <c r="H35" t="n">
-        <v>7058</v>
+        <v>11159</v>
       </c>
       <c r="I35" t="n">
         <v>0.8249316943179235</v>
@@ -2359,14 +2343,30 @@
       <c r="J35" t="b">
         <v>0</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>0.8702040816326531</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.5805902613095306</v>
+      </c>
+      <c r="M35" t="n">
+        <v>39</v>
+      </c>
+      <c r="N35" t="n">
+        <v>45</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1470</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1476</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.9221139444327839</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2727,31 +2727,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Osteoarthritis</t>
+          <t>Colon diverticulosis</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8_Also_Prechondral_Mesenchyme</t>
+          <t>Pooled_epidermis</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.985393658710367</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G43" t="n">
-        <v>76</v>
+        <v>401</v>
       </c>
       <c r="H43" t="n">
-        <v>6948</v>
+        <v>9681</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -2771,31 +2771,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Acne vulgaris</t>
+          <t>Sleep apnea</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Keratinocytes</t>
+          <t>Cortical_organoids_d100</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.032620320855615</v>
+        <v>0.9156060084852654</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>850</v>
+        <v>2907</v>
       </c>
       <c r="H44" t="n">
-        <v>9655</v>
+        <v>7985</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -2820,26 +2820,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pooled_fibroblasts</t>
+          <t>HF_Sebocytes</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.8580126114372689</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
-        <v>1095</v>
+        <v>70</v>
       </c>
       <c r="H45" t="n">
-        <v>9865</v>
+        <v>5404</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -2859,31 +2859,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovarian polycystic syndrome (PCOS)</t>
+          <t>Sleep apnea</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d100</t>
+          <t>Cortical_organoids_d50</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.7489445538981143</v>
+        <v>0.7101074031453778</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7721074750517859</v>
+        <v>0.7626901108875515</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
-        <v>2907</v>
+        <v>3476</v>
       </c>
       <c r="H46" t="n">
-        <v>7983</v>
+        <v>7405</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
@@ -2903,31 +2903,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aneurysm</t>
+          <t>Sleep apnea</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pooled_fibroblasts</t>
+          <t>Skeletal_myocyte_(SKM)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.092683467797832</v>
+        <v>0.9494549058473737</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7834449794144795</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>1093</v>
+        <v>3027</v>
       </c>
       <c r="H47" t="n">
-        <v>9853</v>
+        <v>11496</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -2947,31 +2947,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bronchial asthma</t>
+          <t>Sleep apnea</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Skeletal_myocyte_(SKM)</t>
+          <t>Cortical_organoids_d150</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9583581507957776</v>
+        <v>0.8086458333333333</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7933947164465431</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>289</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
-        <v>2957</v>
+        <v>2880</v>
       </c>
       <c r="H48" t="n">
-        <v>11219</v>
+        <v>7763</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
@@ -2979,44 +2979,28 @@
       <c r="J48" t="b">
         <v>0</v>
       </c>
-      <c r="K48" t="n">
-        <v>1.096785471496552</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.723448293904273</v>
-      </c>
-      <c r="M48" t="n">
-        <v>38</v>
-      </c>
-      <c r="N48" t="n">
-        <v>35</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1471</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1486</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.9408173212354329</v>
-      </c>
-      <c r="R48" t="b">
-        <v>0</v>
-      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Colon diverticulosis</t>
+          <t>Acne vulgaris</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pooled_epidermis</t>
+          <t>Pooled_fibroblasts</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.985393658710367</v>
+        <v>0.8580126114372689</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
@@ -3025,13 +3009,13 @@
         <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G49" t="n">
-        <v>401</v>
+        <v>1095</v>
       </c>
       <c r="H49" t="n">
-        <v>9681</v>
+        <v>9865</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -3051,31 +3035,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Scoliosis</t>
+          <t>carcinoma</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9_Chondrocytes</t>
+          <t>Hepatocyte_Progenitor_(HP)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.6099667774086379</v>
+        <v>0.9987109652706972</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7730263349053912</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>438</v>
       </c>
       <c r="F50" t="n">
-        <v>215</v>
+        <v>568</v>
       </c>
       <c r="G50" t="n">
-        <v>105</v>
+        <v>5567</v>
       </c>
       <c r="H50" t="n">
-        <v>6885</v>
+        <v>7210</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
@@ -3083,43 +3067,59 @@
       <c r="J50" t="b">
         <v>0</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>1.073898606097515</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.4873909825454742</v>
+      </c>
+      <c r="M50" t="n">
+        <v>227</v>
+      </c>
+      <c r="N50" t="n">
+        <v>211</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2786</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2781</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.9221139444327839</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Back Disorders</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Keratinocytes</t>
+          <t>8_Also_Prechondral_Mesenchyme</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.082292018462231</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8234780967067024</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G51" t="n">
-        <v>846</v>
+        <v>76</v>
       </c>
       <c r="H51" t="n">
-        <v>9614</v>
+        <v>6945</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
@@ -3139,31 +3139,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Osteoporosis</t>
+          <t>Acne vulgaris</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9_Chondrocytes</t>
+          <t>Keratinocytes</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1.032620320855615</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G52" t="n">
-        <v>107</v>
+        <v>850</v>
       </c>
       <c r="H52" t="n">
-        <v>7089</v>
+        <v>9655</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -3183,31 +3183,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sleep apnea</t>
+          <t>Psoriasis</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Skeletal_myocyte_(SKM)</t>
+          <t>Keratinocytes</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.9494549058473737</v>
+        <v>1.082292018462231</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0.8234780967067024</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="G53" t="n">
-        <v>3027</v>
+        <v>846</v>
       </c>
       <c r="H53" t="n">
-        <v>11496</v>
+        <v>9614</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -3227,31 +3227,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>carcinoma</t>
+          <t>aneurysm</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hepatocyte_Progenitor_(HP)</t>
+          <t>Pooled_fibroblasts</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.9987109652706972</v>
+        <v>1.092683467797832</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0.7834449794144795</v>
       </c>
       <c r="E54" t="n">
-        <v>438</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
-        <v>568</v>
+        <v>33</v>
       </c>
       <c r="G54" t="n">
-        <v>5567</v>
+        <v>1093</v>
       </c>
       <c r="H54" t="n">
-        <v>7210</v>
+        <v>9853</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -3259,59 +3259,43 @@
       <c r="J54" t="b">
         <v>0</v>
       </c>
-      <c r="K54" t="n">
-        <v>1.073898606097515</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0.4873909825454742</v>
-      </c>
-      <c r="M54" t="n">
-        <v>227</v>
-      </c>
-      <c r="N54" t="n">
-        <v>211</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2786</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2781</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.9221139444327839</v>
-      </c>
-      <c r="R54" t="b">
-        <v>0</v>
-      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sleep apnea</t>
+          <t>Scoliosis</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d50</t>
+          <t>9_Chondrocytes</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.7101074031453778</v>
+        <v>0.6099667774086379</v>
       </c>
       <c r="D55" t="n">
-        <v>0.7626901108875515</v>
+        <v>0.7730263349053912</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>9</v>
+        <v>215</v>
       </c>
       <c r="G55" t="n">
-        <v>3476</v>
+        <v>105</v>
       </c>
       <c r="H55" t="n">
-        <v>7405</v>
+        <v>6885</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -3331,31 +3315,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sleep apnea</t>
+          <t>Bronchial asthma</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d100</t>
+          <t>Skeletal_myocyte_(SKM)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.9156060084852654</v>
+        <v>0.9583581507957776</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0.7933947164465431</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
-        <v>9</v>
+        <v>289</v>
       </c>
       <c r="G56" t="n">
-        <v>2907</v>
+        <v>2957</v>
       </c>
       <c r="H56" t="n">
-        <v>7985</v>
+        <v>11219</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -3363,43 +3347,59 @@
       <c r="J56" t="b">
         <v>0</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>1.096785471496552</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.723448293904273</v>
+      </c>
+      <c r="M56" t="n">
+        <v>38</v>
+      </c>
+      <c r="N56" t="n">
+        <v>35</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1471</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1486</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.9408173212354329</v>
+      </c>
+      <c r="R56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sleep apnea</t>
+          <t>Ovarian polycystic syndrome (PCOS)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cortical_organoids_d150</t>
+          <t>Cortical_organoids_d100</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.8086458333333333</v>
+        <v>0.7489445538981143</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0.7721074750517859</v>
       </c>
       <c r="E57" t="n">
         <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G57" t="n">
-        <v>2880</v>
+        <v>2907</v>
       </c>
       <c r="H57" t="n">
-        <v>7763</v>
+        <v>7983</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -3419,7 +3419,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Back Disorders</t>
+          <t>Osteoarthritis</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3437,13 +3437,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G58" t="n">
         <v>76</v>
       </c>
       <c r="H58" t="n">
-        <v>6945</v>
+        <v>6948</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -3463,12 +3463,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Acne vulgaris</t>
+          <t>Osteoporosis</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HF_Sebocytes</t>
+          <t>9_Chondrocytes</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3481,13 +3481,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G59" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H59" t="n">
-        <v>5404</v>
+        <v>7089</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
